--- a/docs/02_rtm.xlsx
+++ b/docs/02_rtm.xlsx
@@ -646,9 +646,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -688,9 +688,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -730,9 +730,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -772,9 +772,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -814,9 +814,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -856,9 +856,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -898,9 +898,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -940,9 +940,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -982,9 +982,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -1024,9 +1024,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -1066,9 +1066,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>

--- a/docs/02_rtm.xlsx
+++ b/docs/02_rtm.xlsx
@@ -1108,9 +1108,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -1150,9 +1150,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>

--- a/docs/02_rtm.xlsx
+++ b/docs/02_rtm.xlsx
@@ -1192,9 +1192,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -1234,9 +1234,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -1276,9 +1276,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
@@ -1318,9 +1318,9 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Automated</t>
         </is>
       </c>
     </row>
